--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8531,10 +8531,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119772062</v>
+        <v>119772577</v>
       </c>
       <c r="B67" t="n">
-        <v>95455</v>
+        <v>57463</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8547,34 +8547,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506297</v>
+        <v>506434</v>
       </c>
       <c r="R67" t="n">
-        <v>6675802</v>
+        <v>6675822</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8633,10 +8638,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119772577</v>
+        <v>119772062</v>
       </c>
       <c r="B68" t="n">
-        <v>57463</v>
+        <v>95455</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8649,39 +8654,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506434</v>
+        <v>506297</v>
       </c>
       <c r="R68" t="n">
-        <v>6675822</v>
+        <v>6675802</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8409,10 +8409,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119771519</v>
+        <v>119772469</v>
       </c>
       <c r="B66" t="n">
-        <v>95455</v>
+        <v>90527</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8421,38 +8421,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506241</v>
+        <v>506350</v>
       </c>
       <c r="R66" t="n">
-        <v>6675493</v>
+        <v>6675833</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8495,26 +8495,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8531,10 +8511,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119772577</v>
+        <v>119772535</v>
       </c>
       <c r="B67" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8543,43 +8523,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506434</v>
+        <v>506354</v>
       </c>
       <c r="R67" t="n">
-        <v>6675822</v>
+        <v>6675826</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8638,7 +8613,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119772062</v>
+        <v>119772818</v>
       </c>
       <c r="B68" t="n">
         <v>95455</v>
@@ -8678,10 +8653,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506297</v>
+        <v>506325</v>
       </c>
       <c r="R68" t="n">
-        <v>6675802</v>
+        <v>6675898</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8740,10 +8715,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119771792</v>
+        <v>119771969</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8752,47 +8727,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506259</v>
+        <v>506273</v>
       </c>
       <c r="R69" t="n">
-        <v>6675628</v>
+        <v>6675702</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8851,10 +8817,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119771445</v>
+        <v>119771632</v>
       </c>
       <c r="B70" t="n">
-        <v>90334</v>
+        <v>90527</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8867,21 +8833,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8891,10 +8857,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506225</v>
+        <v>506259</v>
       </c>
       <c r="R70" t="n">
-        <v>6675439</v>
+        <v>6675530</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8953,10 +8919,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119772889</v>
+        <v>119771627</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8965,38 +8931,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506306</v>
+        <v>506259</v>
       </c>
       <c r="R71" t="n">
-        <v>6675891</v>
+        <v>6675530</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9055,10 +9021,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119772656</v>
+        <v>119772577</v>
       </c>
       <c r="B72" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9067,35 +9033,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9104,10 +9066,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506388</v>
+        <v>506434</v>
       </c>
       <c r="R72" t="n">
-        <v>6675861</v>
+        <v>6675822</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9166,10 +9128,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119772706</v>
+        <v>119772062</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9178,25 +9140,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9206,10 +9168,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506357</v>
+        <v>506297</v>
       </c>
       <c r="R73" t="n">
-        <v>6675871</v>
+        <v>6675802</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9268,10 +9230,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119771969</v>
+        <v>119772656</v>
       </c>
       <c r="B74" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9280,38 +9242,47 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506273</v>
+        <v>506388</v>
       </c>
       <c r="R74" t="n">
-        <v>6675702</v>
+        <v>6675861</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9370,10 +9341,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119772818</v>
+        <v>119772889</v>
       </c>
       <c r="B75" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9382,25 +9353,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9410,10 +9381,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506325</v>
+        <v>506306</v>
       </c>
       <c r="R75" t="n">
-        <v>6675898</v>
+        <v>6675891</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9472,10 +9443,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119772469</v>
+        <v>119773126</v>
       </c>
       <c r="B76" t="n">
-        <v>90527</v>
+        <v>91863</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9484,25 +9455,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9512,10 +9483,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506350</v>
+        <v>506271</v>
       </c>
       <c r="R76" t="n">
-        <v>6675833</v>
+        <v>6675769</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9574,10 +9545,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119773126</v>
+        <v>119771118</v>
       </c>
       <c r="B77" t="n">
-        <v>91863</v>
+        <v>97907</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9586,38 +9557,47 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Hagmossen, Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506271</v>
+        <v>506342</v>
       </c>
       <c r="R77" t="n">
-        <v>6675769</v>
+        <v>6675315</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9676,7 +9656,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119771865</v>
+        <v>119772795</v>
       </c>
       <c r="B78" t="n">
         <v>97907</v>
@@ -9716,10 +9696,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506261</v>
+        <v>506331</v>
       </c>
       <c r="R78" t="n">
-        <v>6675683</v>
+        <v>6675901</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9778,10 +9758,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119772296</v>
+        <v>119771445</v>
       </c>
       <c r="B79" t="n">
-        <v>91494</v>
+        <v>90334</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9794,34 +9774,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506316</v>
+        <v>506225</v>
       </c>
       <c r="R79" t="n">
-        <v>6675833</v>
+        <v>6675439</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9880,10 +9860,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119771632</v>
+        <v>119772464</v>
       </c>
       <c r="B80" t="n">
-        <v>90527</v>
+        <v>95455</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9892,38 +9872,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506259</v>
+        <v>506350</v>
       </c>
       <c r="R80" t="n">
-        <v>6675530</v>
+        <v>6675833</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9982,10 +9962,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119772464</v>
+        <v>119772296</v>
       </c>
       <c r="B81" t="n">
-        <v>95455</v>
+        <v>91494</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9994,25 +9974,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>4769</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10022,7 +10002,7 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506350</v>
+        <v>506316</v>
       </c>
       <c r="R81" t="n">
         <v>6675833</v>
@@ -10084,7 +10064,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119771118</v>
+        <v>119772706</v>
       </c>
       <c r="B82" t="n">
         <v>97907</v>
@@ -10117,26 +10097,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hagmossen, Hagmossen, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506342</v>
+        <v>506357</v>
       </c>
       <c r="R82" t="n">
-        <v>6675315</v>
+        <v>6675871</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10195,7 +10166,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119772795</v>
+        <v>119771865</v>
       </c>
       <c r="B83" t="n">
         <v>97907</v>
@@ -10235,10 +10206,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506331</v>
+        <v>506261</v>
       </c>
       <c r="R83" t="n">
-        <v>6675901</v>
+        <v>6675683</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10297,10 +10268,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119771627</v>
+        <v>119771519</v>
       </c>
       <c r="B84" t="n">
-        <v>90846</v>
+        <v>95455</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10313,21 +10284,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10337,10 +10308,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506259</v>
+        <v>506241</v>
       </c>
       <c r="R84" t="n">
-        <v>6675530</v>
+        <v>6675493</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10383,6 +10354,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10399,7 +10390,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119772535</v>
+        <v>119771792</v>
       </c>
       <c r="B85" t="n">
         <v>97907</v>
@@ -10432,17 +10423,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506354</v>
+        <v>506259</v>
       </c>
       <c r="R85" t="n">
-        <v>6675826</v>
+        <v>6675628</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8613,10 +8613,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119772818</v>
+        <v>119771969</v>
       </c>
       <c r="B68" t="n">
-        <v>95455</v>
+        <v>95202</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8625,25 +8625,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>53</v>
+        <v>2869</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506325</v>
+        <v>506273</v>
       </c>
       <c r="R68" t="n">
-        <v>6675898</v>
+        <v>6675702</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119771969</v>
+        <v>119771632</v>
       </c>
       <c r="B69" t="n">
-        <v>95202</v>
+        <v>90527</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8731,34 +8731,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2869</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506273</v>
+        <v>506259</v>
       </c>
       <c r="R69" t="n">
-        <v>6675702</v>
+        <v>6675530</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119771632</v>
+        <v>119772818</v>
       </c>
       <c r="B70" t="n">
-        <v>90527</v>
+        <v>95455</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8829,38 +8829,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506259</v>
+        <v>506325</v>
       </c>
       <c r="R70" t="n">
-        <v>6675530</v>
+        <v>6675898</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8409,10 +8409,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119772469</v>
+        <v>119771969</v>
       </c>
       <c r="B66" t="n">
-        <v>90527</v>
+        <v>95202</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8425,21 +8425,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>2869</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8449,10 +8449,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506350</v>
+        <v>506273</v>
       </c>
       <c r="R66" t="n">
-        <v>6675833</v>
+        <v>6675702</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8511,10 +8511,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119772535</v>
+        <v>119771445</v>
       </c>
       <c r="B67" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8523,38 +8523,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506354</v>
+        <v>506225</v>
       </c>
       <c r="R67" t="n">
-        <v>6675826</v>
+        <v>6675439</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8613,10 +8613,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119771969</v>
+        <v>119772296</v>
       </c>
       <c r="B68" t="n">
-        <v>95202</v>
+        <v>91494</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8629,21 +8629,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2869</v>
+        <v>4769</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8653,10 +8653,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506273</v>
+        <v>506316</v>
       </c>
       <c r="R68" t="n">
-        <v>6675702</v>
+        <v>6675833</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8715,10 +8715,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119771632</v>
+        <v>119771865</v>
       </c>
       <c r="B69" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8727,38 +8727,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506259</v>
+        <v>506261</v>
       </c>
       <c r="R69" t="n">
-        <v>6675530</v>
+        <v>6675683</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119772818</v>
+        <v>119771627</v>
       </c>
       <c r="B70" t="n">
-        <v>95455</v>
+        <v>90846</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8833,34 +8833,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506325</v>
+        <v>506259</v>
       </c>
       <c r="R70" t="n">
-        <v>6675898</v>
+        <v>6675530</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8919,10 +8919,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119771627</v>
+        <v>119771632</v>
       </c>
       <c r="B71" t="n">
-        <v>90846</v>
+        <v>90527</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8931,25 +8931,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -9128,10 +9128,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119772062</v>
+        <v>119772795</v>
       </c>
       <c r="B73" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9140,25 +9140,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9168,10 +9168,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506297</v>
+        <v>506331</v>
       </c>
       <c r="R73" t="n">
-        <v>6675802</v>
+        <v>6675901</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9230,7 +9230,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119772656</v>
+        <v>119772535</v>
       </c>
       <c r="B74" t="n">
         <v>97907</v>
@@ -9263,26 +9263,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506388</v>
+        <v>506354</v>
       </c>
       <c r="R74" t="n">
-        <v>6675861</v>
+        <v>6675826</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9341,7 +9332,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119772889</v>
+        <v>119771792</v>
       </c>
       <c r="B75" t="n">
         <v>97907</v>
@@ -9374,17 +9365,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506306</v>
+        <v>506259</v>
       </c>
       <c r="R75" t="n">
-        <v>6675891</v>
+        <v>6675628</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9443,10 +9443,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119773126</v>
+        <v>119772706</v>
       </c>
       <c r="B76" t="n">
-        <v>91863</v>
+        <v>97907</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9455,25 +9455,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9483,10 +9483,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506271</v>
+        <v>506357</v>
       </c>
       <c r="R76" t="n">
-        <v>6675769</v>
+        <v>6675871</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9545,10 +9545,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119771118</v>
+        <v>119772469</v>
       </c>
       <c r="B77" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9557,47 +9557,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hagmossen, Hagmossen, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506342</v>
+        <v>506350</v>
       </c>
       <c r="R77" t="n">
-        <v>6675315</v>
+        <v>6675833</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9656,10 +9647,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119772795</v>
+        <v>119773126</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>91863</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9668,25 +9659,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9696,10 +9687,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506331</v>
+        <v>506271</v>
       </c>
       <c r="R78" t="n">
-        <v>6675901</v>
+        <v>6675769</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9758,10 +9749,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119771445</v>
+        <v>119772464</v>
       </c>
       <c r="B79" t="n">
-        <v>90334</v>
+        <v>95455</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9770,38 +9761,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506225</v>
+        <v>506350</v>
       </c>
       <c r="R79" t="n">
-        <v>6675439</v>
+        <v>6675833</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9860,7 +9851,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119772464</v>
+        <v>119772062</v>
       </c>
       <c r="B80" t="n">
         <v>95455</v>
@@ -9900,10 +9891,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506350</v>
+        <v>506297</v>
       </c>
       <c r="R80" t="n">
-        <v>6675833</v>
+        <v>6675802</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9962,10 +9953,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119772296</v>
+        <v>119772889</v>
       </c>
       <c r="B81" t="n">
-        <v>91494</v>
+        <v>97907</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9974,25 +9965,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10002,10 +9993,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506316</v>
+        <v>506306</v>
       </c>
       <c r="R81" t="n">
-        <v>6675833</v>
+        <v>6675891</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10064,7 +10055,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119772706</v>
+        <v>119771118</v>
       </c>
       <c r="B82" t="n">
         <v>97907</v>
@@ -10097,17 +10088,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Hagmossen, Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506357</v>
+        <v>506342</v>
       </c>
       <c r="R82" t="n">
-        <v>6675871</v>
+        <v>6675315</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10166,7 +10166,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119771865</v>
+        <v>119772656</v>
       </c>
       <c r="B83" t="n">
         <v>97907</v>
@@ -10199,17 +10199,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506261</v>
+        <v>506388</v>
       </c>
       <c r="R83" t="n">
-        <v>6675683</v>
+        <v>6675861</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10268,7 +10277,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119771519</v>
+        <v>119772818</v>
       </c>
       <c r="B84" t="n">
         <v>95455</v>
@@ -10304,14 +10313,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506241</v>
+        <v>506325</v>
       </c>
       <c r="R84" t="n">
-        <v>6675493</v>
+        <v>6675898</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10354,26 +10363,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10390,10 +10379,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119771792</v>
+        <v>119771519</v>
       </c>
       <c r="B85" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10402,47 +10391,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506259</v>
+        <v>506241</v>
       </c>
       <c r="R85" t="n">
-        <v>6675628</v>
+        <v>6675493</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10485,6 +10465,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8409,10 +8409,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119771969</v>
+        <v>119772656</v>
       </c>
       <c r="B66" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8421,38 +8421,47 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506273</v>
+        <v>506388</v>
       </c>
       <c r="R66" t="n">
-        <v>6675702</v>
+        <v>6675861</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8511,10 +8520,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119771445</v>
+        <v>119772296</v>
       </c>
       <c r="B67" t="n">
-        <v>90334</v>
+        <v>91494</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8527,34 +8536,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506225</v>
+        <v>506316</v>
       </c>
       <c r="R67" t="n">
-        <v>6675439</v>
+        <v>6675833</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8613,10 +8622,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119772296</v>
+        <v>119772706</v>
       </c>
       <c r="B68" t="n">
-        <v>91494</v>
+        <v>97907</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8625,25 +8634,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8653,10 +8662,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506316</v>
+        <v>506357</v>
       </c>
       <c r="R68" t="n">
-        <v>6675833</v>
+        <v>6675871</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8715,10 +8724,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119771865</v>
+        <v>119772062</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8727,25 +8736,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8755,10 +8764,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506261</v>
+        <v>506297</v>
       </c>
       <c r="R69" t="n">
-        <v>6675683</v>
+        <v>6675802</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8817,10 +8826,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119771627</v>
+        <v>119772535</v>
       </c>
       <c r="B70" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8829,38 +8838,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506259</v>
+        <v>506354</v>
       </c>
       <c r="R70" t="n">
-        <v>6675530</v>
+        <v>6675826</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8919,10 +8928,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119771632</v>
+        <v>119771118</v>
       </c>
       <c r="B71" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8931,38 +8940,47 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Hagmossen, Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506259</v>
+        <v>506342</v>
       </c>
       <c r="R71" t="n">
-        <v>6675530</v>
+        <v>6675315</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9021,10 +9039,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119772577</v>
+        <v>119771969</v>
       </c>
       <c r="B72" t="n">
-        <v>57463</v>
+        <v>95202</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9033,43 +9051,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>2869</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506434</v>
+        <v>506273</v>
       </c>
       <c r="R72" t="n">
-        <v>6675822</v>
+        <v>6675702</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9128,10 +9141,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119772795</v>
+        <v>119772818</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9140,25 +9153,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9168,10 +9181,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506331</v>
+        <v>506325</v>
       </c>
       <c r="R73" t="n">
-        <v>6675901</v>
+        <v>6675898</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9230,10 +9243,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119772535</v>
+        <v>119772469</v>
       </c>
       <c r="B74" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9242,25 +9255,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9270,10 +9283,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506354</v>
+        <v>506350</v>
       </c>
       <c r="R74" t="n">
-        <v>6675826</v>
+        <v>6675833</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9332,7 +9345,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119771792</v>
+        <v>119772889</v>
       </c>
       <c r="B75" t="n">
         <v>97907</v>
@@ -9365,26 +9378,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506259</v>
+        <v>506306</v>
       </c>
       <c r="R75" t="n">
-        <v>6675628</v>
+        <v>6675891</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9443,7 +9447,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119772706</v>
+        <v>119771792</v>
       </c>
       <c r="B76" t="n">
         <v>97907</v>
@@ -9476,17 +9480,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506357</v>
+        <v>506259</v>
       </c>
       <c r="R76" t="n">
-        <v>6675871</v>
+        <v>6675628</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9545,7 +9558,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119772469</v>
+        <v>119771632</v>
       </c>
       <c r="B77" t="n">
         <v>90527</v>
@@ -9581,14 +9594,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506350</v>
+        <v>506259</v>
       </c>
       <c r="R77" t="n">
-        <v>6675833</v>
+        <v>6675530</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9647,10 +9660,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119773126</v>
+        <v>119771519</v>
       </c>
       <c r="B78" t="n">
-        <v>91863</v>
+        <v>95455</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9663,34 +9676,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506271</v>
+        <v>506241</v>
       </c>
       <c r="R78" t="n">
-        <v>6675769</v>
+        <v>6675493</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9733,6 +9746,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9749,10 +9782,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119772464</v>
+        <v>119772795</v>
       </c>
       <c r="B79" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9761,25 +9794,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9789,10 +9822,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506350</v>
+        <v>506331</v>
       </c>
       <c r="R79" t="n">
-        <v>6675833</v>
+        <v>6675901</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9851,10 +9884,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119772062</v>
+        <v>119772577</v>
       </c>
       <c r="B80" t="n">
-        <v>95455</v>
+        <v>57463</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9867,34 +9900,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506297</v>
+        <v>506434</v>
       </c>
       <c r="R80" t="n">
-        <v>6675802</v>
+        <v>6675822</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9953,10 +9991,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119772889</v>
+        <v>119772464</v>
       </c>
       <c r="B81" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9965,25 +10003,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9993,10 +10031,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506306</v>
+        <v>506350</v>
       </c>
       <c r="R81" t="n">
-        <v>6675891</v>
+        <v>6675833</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10055,10 +10093,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119771118</v>
+        <v>119773126</v>
       </c>
       <c r="B82" t="n">
-        <v>97907</v>
+        <v>91863</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10067,47 +10105,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hagmossen, Hagmossen, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506342</v>
+        <v>506271</v>
       </c>
       <c r="R82" t="n">
-        <v>6675315</v>
+        <v>6675769</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10166,10 +10195,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119772656</v>
+        <v>119771445</v>
       </c>
       <c r="B83" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10178,47 +10207,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506388</v>
+        <v>506225</v>
       </c>
       <c r="R83" t="n">
-        <v>6675861</v>
+        <v>6675439</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10277,10 +10297,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119772818</v>
+        <v>119771627</v>
       </c>
       <c r="B84" t="n">
-        <v>95455</v>
+        <v>90846</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10293,34 +10313,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506325</v>
+        <v>506259</v>
       </c>
       <c r="R84" t="n">
-        <v>6675898</v>
+        <v>6675530</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10379,10 +10399,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119771519</v>
+        <v>119771865</v>
       </c>
       <c r="B85" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10391,38 +10411,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506241</v>
+        <v>506261</v>
       </c>
       <c r="R85" t="n">
-        <v>6675493</v>
+        <v>6675683</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10465,26 +10485,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8520,10 +8520,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119772296</v>
+        <v>119772706</v>
       </c>
       <c r="B67" t="n">
-        <v>91494</v>
+        <v>97907</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8532,25 +8532,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506316</v>
+        <v>506357</v>
       </c>
       <c r="R67" t="n">
-        <v>6675833</v>
+        <v>6675871</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8622,10 +8622,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119772706</v>
+        <v>119772296</v>
       </c>
       <c r="B68" t="n">
-        <v>97907</v>
+        <v>91494</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8634,25 +8634,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8662,10 +8662,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506357</v>
+        <v>506316</v>
       </c>
       <c r="R68" t="n">
-        <v>6675871</v>
+        <v>6675833</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9243,10 +9243,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119772469</v>
+        <v>119772889</v>
       </c>
       <c r="B74" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9255,25 +9255,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9283,10 +9283,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506350</v>
+        <v>506306</v>
       </c>
       <c r="R74" t="n">
-        <v>6675833</v>
+        <v>6675891</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9345,10 +9345,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119772889</v>
+        <v>119772469</v>
       </c>
       <c r="B75" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9357,25 +9357,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9385,10 +9385,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506306</v>
+        <v>506350</v>
       </c>
       <c r="R75" t="n">
-        <v>6675891</v>
+        <v>6675833</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9558,10 +9558,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119771632</v>
+        <v>119771519</v>
       </c>
       <c r="B77" t="n">
-        <v>90527</v>
+        <v>95455</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9570,25 +9570,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506259</v>
+        <v>506241</v>
       </c>
       <c r="R77" t="n">
-        <v>6675530</v>
+        <v>6675493</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9644,6 +9644,26 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9660,10 +9680,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119771519</v>
+        <v>119771632</v>
       </c>
       <c r="B78" t="n">
-        <v>95455</v>
+        <v>90527</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9672,25 +9692,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9700,10 +9720,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506241</v>
+        <v>506259</v>
       </c>
       <c r="R78" t="n">
-        <v>6675493</v>
+        <v>6675530</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9746,26 +9766,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9991,10 +9991,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119772464</v>
+        <v>119771445</v>
       </c>
       <c r="B81" t="n">
-        <v>95455</v>
+        <v>90334</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10003,38 +10003,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506350</v>
+        <v>506225</v>
       </c>
       <c r="R81" t="n">
-        <v>6675833</v>
+        <v>6675439</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10093,10 +10093,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119773126</v>
+        <v>119772464</v>
       </c>
       <c r="B82" t="n">
-        <v>91863</v>
+        <v>95455</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10109,21 +10109,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506271</v>
+        <v>506350</v>
       </c>
       <c r="R82" t="n">
-        <v>6675769</v>
+        <v>6675833</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10195,10 +10195,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119771445</v>
+        <v>119773126</v>
       </c>
       <c r="B83" t="n">
-        <v>90334</v>
+        <v>91863</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10207,38 +10207,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506225</v>
+        <v>506271</v>
       </c>
       <c r="R83" t="n">
-        <v>6675439</v>
+        <v>6675769</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8928,10 +8928,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119771118</v>
+        <v>119771969</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8940,47 +8940,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hagmossen, Hagmossen, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506342</v>
+        <v>506273</v>
       </c>
       <c r="R71" t="n">
-        <v>6675315</v>
+        <v>6675702</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9039,10 +9030,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119771969</v>
+        <v>119771118</v>
       </c>
       <c r="B72" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9051,38 +9042,47 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Hagmossen, Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506273</v>
+        <v>506342</v>
       </c>
       <c r="R72" t="n">
-        <v>6675702</v>
+        <v>6675315</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9243,10 +9243,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119772889</v>
+        <v>119772469</v>
       </c>
       <c r="B74" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9255,25 +9255,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9283,10 +9283,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506306</v>
+        <v>506350</v>
       </c>
       <c r="R74" t="n">
-        <v>6675891</v>
+        <v>6675833</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9345,10 +9345,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119772469</v>
+        <v>119772889</v>
       </c>
       <c r="B75" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9357,25 +9357,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9385,10 +9385,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506350</v>
+        <v>506306</v>
       </c>
       <c r="R75" t="n">
-        <v>6675833</v>
+        <v>6675891</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10093,10 +10093,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119772464</v>
+        <v>119773126</v>
       </c>
       <c r="B82" t="n">
-        <v>95455</v>
+        <v>91863</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10109,21 +10109,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506350</v>
+        <v>506271</v>
       </c>
       <c r="R82" t="n">
-        <v>6675833</v>
+        <v>6675769</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10195,10 +10195,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119773126</v>
+        <v>119772464</v>
       </c>
       <c r="B83" t="n">
-        <v>91863</v>
+        <v>95455</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10211,21 +10211,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10235,10 +10235,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506271</v>
+        <v>506350</v>
       </c>
       <c r="R83" t="n">
-        <v>6675769</v>
+        <v>6675833</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8928,10 +8928,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119771969</v>
+        <v>119771118</v>
       </c>
       <c r="B71" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8940,38 +8940,47 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Hagmossen, Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506273</v>
+        <v>506342</v>
       </c>
       <c r="R71" t="n">
-        <v>6675702</v>
+        <v>6675315</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9030,10 +9039,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119771118</v>
+        <v>119771969</v>
       </c>
       <c r="B72" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9042,47 +9051,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hagmossen, Hagmossen, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506342</v>
+        <v>506273</v>
       </c>
       <c r="R72" t="n">
-        <v>6675315</v>
+        <v>6675702</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9558,10 +9558,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119771519</v>
+        <v>119771632</v>
       </c>
       <c r="B77" t="n">
-        <v>95455</v>
+        <v>90527</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9570,25 +9570,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506241</v>
+        <v>506259</v>
       </c>
       <c r="R77" t="n">
-        <v>6675493</v>
+        <v>6675530</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9644,26 +9644,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9680,10 +9660,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119771632</v>
+        <v>119771519</v>
       </c>
       <c r="B78" t="n">
-        <v>90527</v>
+        <v>95455</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9692,25 +9672,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9720,10 +9700,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506259</v>
+        <v>506241</v>
       </c>
       <c r="R78" t="n">
-        <v>6675530</v>
+        <v>6675493</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9766,6 +9746,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -10093,10 +10093,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119773126</v>
+        <v>119772464</v>
       </c>
       <c r="B82" t="n">
-        <v>91863</v>
+        <v>95455</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10109,21 +10109,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506271</v>
+        <v>506350</v>
       </c>
       <c r="R82" t="n">
-        <v>6675769</v>
+        <v>6675833</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10195,10 +10195,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119772464</v>
+        <v>119773126</v>
       </c>
       <c r="B83" t="n">
-        <v>95455</v>
+        <v>91863</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10211,21 +10211,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10235,10 +10235,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506350</v>
+        <v>506271</v>
       </c>
       <c r="R83" t="n">
-        <v>6675833</v>
+        <v>6675769</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8928,10 +8928,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119771118</v>
+        <v>119771969</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
+        <v>95202</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8940,47 +8940,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hagmossen, Hagmossen, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506342</v>
+        <v>506273</v>
       </c>
       <c r="R71" t="n">
-        <v>6675315</v>
+        <v>6675702</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9039,10 +9030,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119771969</v>
+        <v>119771118</v>
       </c>
       <c r="B72" t="n">
-        <v>95202</v>
+        <v>97907</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9051,38 +9042,47 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Hagmossen, Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506273</v>
+        <v>506342</v>
       </c>
       <c r="R72" t="n">
-        <v>6675702</v>
+        <v>6675315</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -10093,10 +10093,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119772464</v>
+        <v>119773126</v>
       </c>
       <c r="B82" t="n">
-        <v>95455</v>
+        <v>91863</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10109,21 +10109,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506350</v>
+        <v>506271</v>
       </c>
       <c r="R82" t="n">
-        <v>6675833</v>
+        <v>6675769</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10195,10 +10195,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119773126</v>
+        <v>119772464</v>
       </c>
       <c r="B83" t="n">
-        <v>91863</v>
+        <v>95455</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10211,21 +10211,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10235,10 +10235,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506271</v>
+        <v>506350</v>
       </c>
       <c r="R83" t="n">
-        <v>6675769</v>
+        <v>6675833</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8409,10 +8409,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119772656</v>
+        <v>119771519</v>
       </c>
       <c r="B66" t="n">
-        <v>97907</v>
+        <v>95478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8421,47 +8421,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506388</v>
+        <v>506241</v>
       </c>
       <c r="R66" t="n">
-        <v>6675861</v>
+        <v>6675493</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8504,6 +8495,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8520,10 +8531,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119772706</v>
+        <v>119773126</v>
       </c>
       <c r="B67" t="n">
-        <v>97907</v>
+        <v>91881</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8532,25 +8543,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8560,10 +8571,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506357</v>
+        <v>506271</v>
       </c>
       <c r="R67" t="n">
-        <v>6675871</v>
+        <v>6675769</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8622,10 +8633,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119772296</v>
+        <v>119772889</v>
       </c>
       <c r="B68" t="n">
-        <v>91494</v>
+        <v>97930</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8634,25 +8645,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8662,10 +8673,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506316</v>
+        <v>506306</v>
       </c>
       <c r="R68" t="n">
-        <v>6675833</v>
+        <v>6675891</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8724,10 +8735,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119772062</v>
+        <v>119771632</v>
       </c>
       <c r="B69" t="n">
-        <v>95455</v>
+        <v>90545</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8736,38 +8747,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506297</v>
+        <v>506259</v>
       </c>
       <c r="R69" t="n">
-        <v>6675802</v>
+        <v>6675530</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8826,10 +8837,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119772535</v>
+        <v>119771969</v>
       </c>
       <c r="B70" t="n">
-        <v>97907</v>
+        <v>95225</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8838,25 +8849,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8866,10 +8877,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506354</v>
+        <v>506273</v>
       </c>
       <c r="R70" t="n">
-        <v>6675826</v>
+        <v>6675702</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8928,10 +8939,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119771969</v>
+        <v>119771792</v>
       </c>
       <c r="B71" t="n">
-        <v>95202</v>
+        <v>97930</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8940,38 +8951,47 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506273</v>
+        <v>506259</v>
       </c>
       <c r="R71" t="n">
-        <v>6675702</v>
+        <v>6675628</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9030,10 +9050,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119771118</v>
+        <v>119772656</v>
       </c>
       <c r="B72" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9065,24 +9085,24 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hagmossen, Hagmossen, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506342</v>
+        <v>506388</v>
       </c>
       <c r="R72" t="n">
-        <v>6675315</v>
+        <v>6675861</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9144,7 +9164,7 @@
         <v>119772818</v>
       </c>
       <c r="B73" t="n">
-        <v>95455</v>
+        <v>95478</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9243,10 +9263,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119772469</v>
+        <v>119772577</v>
       </c>
       <c r="B74" t="n">
-        <v>90527</v>
+        <v>57473</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9255,38 +9275,43 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506350</v>
+        <v>506434</v>
       </c>
       <c r="R74" t="n">
-        <v>6675833</v>
+        <v>6675822</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9345,10 +9370,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119772889</v>
+        <v>119772469</v>
       </c>
       <c r="B75" t="n">
-        <v>97907</v>
+        <v>90545</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9357,25 +9382,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9385,10 +9410,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506306</v>
+        <v>506350</v>
       </c>
       <c r="R75" t="n">
-        <v>6675891</v>
+        <v>6675833</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9447,10 +9472,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119771792</v>
+        <v>119772706</v>
       </c>
       <c r="B76" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9480,26 +9505,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506259</v>
+        <v>506357</v>
       </c>
       <c r="R76" t="n">
-        <v>6675628</v>
+        <v>6675871</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9558,10 +9574,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119771632</v>
+        <v>119772795</v>
       </c>
       <c r="B77" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9570,38 +9586,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506259</v>
+        <v>506331</v>
       </c>
       <c r="R77" t="n">
-        <v>6675530</v>
+        <v>6675901</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9660,10 +9676,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119771519</v>
+        <v>119771118</v>
       </c>
       <c r="B78" t="n">
-        <v>95455</v>
+        <v>97930</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9672,38 +9688,47 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Hagmossen, Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506241</v>
+        <v>506342</v>
       </c>
       <c r="R78" t="n">
-        <v>6675493</v>
+        <v>6675315</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9746,26 +9771,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9782,10 +9787,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119772795</v>
+        <v>119771865</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9822,10 +9827,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506331</v>
+        <v>506261</v>
       </c>
       <c r="R79" t="n">
-        <v>6675901</v>
+        <v>6675683</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9884,10 +9889,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119772577</v>
+        <v>119772464</v>
       </c>
       <c r="B80" t="n">
-        <v>57463</v>
+        <v>95478</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9900,39 +9905,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506434</v>
+        <v>506350</v>
       </c>
       <c r="R80" t="n">
-        <v>6675822</v>
+        <v>6675833</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119771445</v>
+        <v>119772535</v>
       </c>
       <c r="B81" t="n">
-        <v>90334</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10003,38 +10003,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506225</v>
+        <v>506354</v>
       </c>
       <c r="R81" t="n">
-        <v>6675439</v>
+        <v>6675826</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10093,10 +10093,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119773126</v>
+        <v>119772062</v>
       </c>
       <c r="B82" t="n">
-        <v>91863</v>
+        <v>95478</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10109,21 +10109,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506271</v>
+        <v>506297</v>
       </c>
       <c r="R82" t="n">
-        <v>6675769</v>
+        <v>6675802</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10195,10 +10195,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119772464</v>
+        <v>119771445</v>
       </c>
       <c r="B83" t="n">
-        <v>95455</v>
+        <v>90351</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10207,38 +10207,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506350</v>
+        <v>506225</v>
       </c>
       <c r="R83" t="n">
-        <v>6675833</v>
+        <v>6675439</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10297,10 +10297,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119771627</v>
+        <v>119772296</v>
       </c>
       <c r="B84" t="n">
-        <v>90846</v>
+        <v>91512</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10309,38 +10309,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506259</v>
+        <v>506316</v>
       </c>
       <c r="R84" t="n">
-        <v>6675530</v>
+        <v>6675833</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10399,10 +10399,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119771865</v>
+        <v>119771627</v>
       </c>
       <c r="B85" t="n">
-        <v>97907</v>
+        <v>90864</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10411,38 +10411,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>506261</v>
+        <v>506259</v>
       </c>
       <c r="R85" t="n">
-        <v>6675683</v>
+        <v>6675530</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 29793-2024 artfynd.xlsx
+++ b/artfynd/A 29793-2024 artfynd.xlsx
@@ -8409,10 +8409,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119771519</v>
+        <v>119772469</v>
       </c>
       <c r="B66" t="n">
-        <v>95478</v>
+        <v>90545</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8421,38 +8421,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>506241</v>
+        <v>506350</v>
       </c>
       <c r="R66" t="n">
-        <v>6675493</v>
+        <v>6675833</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8495,26 +8495,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8531,10 +8511,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119773126</v>
+        <v>119771792</v>
       </c>
       <c r="B67" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8543,38 +8523,47 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>506271</v>
+        <v>506259</v>
       </c>
       <c r="R67" t="n">
-        <v>6675769</v>
+        <v>6675628</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8633,10 +8622,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119772889</v>
+        <v>119771445</v>
       </c>
       <c r="B68" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8645,38 +8634,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>506306</v>
+        <v>506225</v>
       </c>
       <c r="R68" t="n">
-        <v>6675891</v>
+        <v>6675439</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8735,10 +8724,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119771632</v>
+        <v>119771519</v>
       </c>
       <c r="B69" t="n">
-        <v>90545</v>
+        <v>95478</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8747,25 +8736,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8775,10 +8764,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>506259</v>
+        <v>506241</v>
       </c>
       <c r="R69" t="n">
-        <v>6675530</v>
+        <v>6675493</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8821,6 +8810,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8837,10 +8846,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119771969</v>
+        <v>119771118</v>
       </c>
       <c r="B70" t="n">
-        <v>95225</v>
+        <v>97930</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8849,38 +8858,47 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Hagmossen, Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>506273</v>
+        <v>506342</v>
       </c>
       <c r="R70" t="n">
-        <v>6675702</v>
+        <v>6675315</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8939,7 +8957,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119771792</v>
+        <v>119772535</v>
       </c>
       <c r="B71" t="n">
         <v>97930</v>
@@ -8972,26 +8990,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>506259</v>
+        <v>506354</v>
       </c>
       <c r="R71" t="n">
-        <v>6675628</v>
+        <v>6675826</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9050,10 +9059,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119772656</v>
+        <v>119772818</v>
       </c>
       <c r="B72" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9062,47 +9071,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>506388</v>
+        <v>506325</v>
       </c>
       <c r="R72" t="n">
-        <v>6675861</v>
+        <v>6675898</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9161,7 +9161,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119772818</v>
+        <v>119772062</v>
       </c>
       <c r="B73" t="n">
         <v>95478</v>
@@ -9201,10 +9201,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>506325</v>
+        <v>506297</v>
       </c>
       <c r="R73" t="n">
-        <v>6675898</v>
+        <v>6675802</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9263,10 +9263,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119772577</v>
+        <v>119771865</v>
       </c>
       <c r="B74" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9275,43 +9275,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>506434</v>
+        <v>506261</v>
       </c>
       <c r="R74" t="n">
-        <v>6675822</v>
+        <v>6675683</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9370,10 +9365,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119772469</v>
+        <v>119772889</v>
       </c>
       <c r="B75" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9382,25 +9377,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9410,10 +9405,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>506350</v>
+        <v>506306</v>
       </c>
       <c r="R75" t="n">
-        <v>6675833</v>
+        <v>6675891</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9472,7 +9467,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119772706</v>
+        <v>119772656</v>
       </c>
       <c r="B76" t="n">
         <v>97930</v>
@@ -9505,17 +9500,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>506357</v>
+        <v>506388</v>
       </c>
       <c r="R76" t="n">
-        <v>6675871</v>
+        <v>6675861</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9574,10 +9578,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119772795</v>
+        <v>119773126</v>
       </c>
       <c r="B77" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9586,25 +9590,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9614,10 +9618,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>506331</v>
+        <v>506271</v>
       </c>
       <c r="R77" t="n">
-        <v>6675901</v>
+        <v>6675769</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9676,10 +9680,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119771118</v>
+        <v>119771969</v>
       </c>
       <c r="B78" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9688,47 +9692,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hagmossen, Hagmossen, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>506342</v>
+        <v>506273</v>
       </c>
       <c r="R78" t="n">
-        <v>6675315</v>
+        <v>6675702</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9787,10 +9782,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119771865</v>
+        <v>119772296</v>
       </c>
       <c r="B79" t="n">
-        <v>97930</v>
+        <v>91512</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9799,25 +9794,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9827,10 +9822,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>506261</v>
+        <v>506316</v>
       </c>
       <c r="R79" t="n">
-        <v>6675683</v>
+        <v>6675833</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9889,10 +9884,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119772464</v>
+        <v>119772795</v>
       </c>
       <c r="B80" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9901,25 +9896,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9929,10 +9924,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>506350</v>
+        <v>506331</v>
       </c>
       <c r="R80" t="n">
-        <v>6675833</v>
+        <v>6675901</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9991,10 +9986,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119772535</v>
+        <v>119772577</v>
       </c>
       <c r="B81" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10003,38 +9998,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>506354</v>
+        <v>506434</v>
       </c>
       <c r="R81" t="n">
-        <v>6675826</v>
+        <v>6675822</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10093,10 +10093,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119772062</v>
+        <v>119771627</v>
       </c>
       <c r="B82" t="n">
-        <v>95478</v>
+        <v>90864</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10109,34 +10109,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrviksån, Norrviksån, Dlr</t>
+          <t>Svartkya, Svartkya, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>506297</v>
+        <v>506259</v>
       </c>
       <c r="R82" t="n">
-        <v>6675802</v>
+        <v>6675530</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10195,10 +10195,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119771445</v>
+        <v>119772464</v>
       </c>
       <c r="B83" t="n">
-        <v>90351</v>
+        <v>95478</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10207,38 +10207,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Svartkya, Svartkya, Dlr</t>
+          <t>Norrviksån, Norrviksån, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>506225</v>
+        <v>506350</v>
       </c>
       <c r="R83" t="n">
-        <v>6675439</v>
+        <v>6675833</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10297,10 +10297,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119772296</v>
+        <v>119772706</v>
       </c>
       <c r="B84" t="n">
-        <v>91512</v>
+        <v>97930</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10309,25 +10309,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10337,10 +10337,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>506316</v>
+        <v>506357</v>
       </c>
       <c r="R84" t="n">
-        <v>6675833</v>
+        <v>6675871</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10399,10 +10399,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119771627</v>
+        <v>119771632</v>
       </c>
       <c r="B85" t="n">
-        <v>90864</v>
+        <v>90545</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10411,25 +10411,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
